--- a/assets/files/templates/SafePlum_risk_assessment.xlsx
+++ b/assets/files/templates/SafePlum_risk_assessment.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="96">
   <si>
     <t xml:space="preserve">위험성평가표 — 작성 안내</t>
   </si>
@@ -2199,9 +2199,6 @@
       </rPr>
       <t xml:space="preserve">팀</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-15</t>
   </si>
   <si>
     <r>
@@ -4076,8 +4073,8 @@
       <c r="R7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="S7" s="21" t="s">
-        <v>57</v>
+      <c r="S7" s="21" t="n">
+        <v>46341</v>
       </c>
       <c r="T7" s="22"/>
       <c r="U7" s="15"/>
@@ -4787,7 +4784,7 @@
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -4798,7 +4795,7 @@
         <v>1건</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="24" t="str">
@@ -4808,7 +4805,7 @@
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M28" s="11"/>
       <c r="N28" s="25" t="str">
@@ -4936,7 +4933,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4947,7 +4944,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -4958,22 +4955,22 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>66</v>
-      </c>
       <c r="F4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4981,19 +4978,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>67</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>68</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="27" t="s">
         <v>69</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5001,19 +4998,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>71</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>72</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="27" t="s">
         <v>73</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5021,19 +5018,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>75</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>76</v>
       </c>
       <c r="E7" s="25" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="27" t="s">
         <v>77</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5041,19 +5038,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>79</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>80</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="27" t="s">
         <v>81</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5061,29 +5058,29 @@
         <v>1</v>
       </c>
       <c r="B9" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>83</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5094,10 +5091,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5108,10 +5105,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5122,10 +5119,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5136,10 +5133,10 @@
         <v>15</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5150,15 +5147,15 @@
         <v>20</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="33" t="n">
@@ -5167,12 +5164,12 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="35" t="n">
         <v>4</v>

--- a/assets/files/templates/SafePlum_risk_assessment.xlsx
+++ b/assets/files/templates/SafePlum_risk_assessment.xlsx
@@ -3733,27 +3733,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
@@ -3766,12 +3766,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
@@ -3784,12 +3784,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
         <v>14</v>
       </c>
